--- a/artfynd/A 58191-2024 artfynd.xlsx
+++ b/artfynd/A 58191-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1011,6 +1011,108 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123940042</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57382</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>712287</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6396587</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Morgan Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Morgan Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
